--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/75.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/75.xlsx
@@ -426,13 +426,13 @@
         <v>-21.54871473538681</v>
       </c>
       <c r="E2">
-        <v>-7.422687221316192</v>
+        <v>-7.194343447953422</v>
       </c>
       <c r="F2">
-        <v>-2.102093433083228</v>
+        <v>-2.003057968241534</v>
       </c>
       <c r="G2">
-        <v>-9.80234441244566</v>
+        <v>-8.870041819858264</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.15475146231089</v>
       </c>
       <c r="E3">
-        <v>-7.637033481521253</v>
+        <v>-7.775527802097836</v>
       </c>
       <c r="F3">
-        <v>-1.681076528977782</v>
+        <v>-2.058841885880858</v>
       </c>
       <c r="G3">
-        <v>-9.003605779640161</v>
+        <v>-8.34118879105077</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.76587808047694</v>
       </c>
       <c r="E4">
-        <v>-8.374006398477542</v>
+        <v>-8.381568950070353</v>
       </c>
       <c r="F4">
-        <v>-1.51622810235107</v>
+        <v>-1.812730617039513</v>
       </c>
       <c r="G4">
-        <v>-9.120722949182957</v>
+        <v>-8.719266333817698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-20.42768394975658</v>
       </c>
       <c r="E5">
-        <v>-9.102112563326813</v>
+        <v>-9.857869590466919</v>
       </c>
       <c r="F5">
-        <v>-1.734831774847651</v>
+        <v>-1.918260482319156</v>
       </c>
       <c r="G5">
-        <v>-8.962531841134423</v>
+        <v>-8.453035572095049</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.11260026678056</v>
       </c>
       <c r="E6">
-        <v>-9.954851389815188</v>
+        <v>-9.57616680787177</v>
       </c>
       <c r="F6">
-        <v>-1.532869175105909</v>
+        <v>-1.906385835600026</v>
       </c>
       <c r="G6">
-        <v>-8.697052573249188</v>
+        <v>-7.786003683023914</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-19.8246045251261</v>
       </c>
       <c r="E7">
-        <v>-10.69210507215995</v>
+        <v>-11.48290343117141</v>
       </c>
       <c r="F7">
-        <v>-1.521764081703979</v>
+        <v>-1.833163955764369</v>
       </c>
       <c r="G7">
-        <v>-8.033145839167126</v>
+        <v>-7.939695759684579</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-19.55536528712166</v>
       </c>
       <c r="E8">
-        <v>-12.01527989246115</v>
+        <v>-10.84653056429552</v>
       </c>
       <c r="F8">
-        <v>-1.587684731251361</v>
+        <v>-1.820142848559763</v>
       </c>
       <c r="G8">
-        <v>-8.009379432740698</v>
+        <v>-7.979895714167949</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-19.29080924503879</v>
       </c>
       <c r="E9">
-        <v>-12.40530377331978</v>
+        <v>-12.37686495655161</v>
       </c>
       <c r="F9">
-        <v>-1.635958670016905</v>
+        <v>-1.627723041298272</v>
       </c>
       <c r="G9">
-        <v>-7.882324005489009</v>
+        <v>-7.161644725953986</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-19.01835392947702</v>
       </c>
       <c r="E10">
-        <v>-13.00747760448975</v>
+        <v>-12.61612688074687</v>
       </c>
       <c r="F10">
-        <v>-1.403481500258237</v>
+        <v>-1.55009673198193</v>
       </c>
       <c r="G10">
-        <v>-7.86783043711808</v>
+        <v>-7.231947471025949</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-18.73831120494584</v>
       </c>
       <c r="E11">
-        <v>-13.62714493075134</v>
+        <v>-14.10219091110398</v>
       </c>
       <c r="F11">
-        <v>-1.329300370970139</v>
+        <v>-1.565776070182119</v>
       </c>
       <c r="G11">
-        <v>-7.340129478158253</v>
+        <v>-6.53341574114865</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.44069125995322</v>
       </c>
       <c r="E12">
-        <v>-14.57517190730912</v>
+        <v>-14.26138488636962</v>
       </c>
       <c r="F12">
-        <v>-1.070136516962883</v>
+        <v>-1.533381934528242</v>
       </c>
       <c r="G12">
-        <v>-6.772321259990155</v>
+        <v>-6.085104974766085</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-18.11563348188002</v>
       </c>
       <c r="E13">
-        <v>-15.5665997787564</v>
+        <v>-15.04039109906511</v>
       </c>
       <c r="F13">
-        <v>-1.158612782521092</v>
+        <v>-1.349310413952164</v>
       </c>
       <c r="G13">
-        <v>-5.639349949539837</v>
+        <v>-5.205589030802369</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-17.78056816108369</v>
       </c>
       <c r="E14">
-        <v>-15.96325787403626</v>
+        <v>-16.06423831593331</v>
       </c>
       <c r="F14">
-        <v>-1.327743868620278</v>
+        <v>-1.115762993509079</v>
       </c>
       <c r="G14">
-        <v>-5.804827568320308</v>
+        <v>-5.469608348104786</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-17.44885235368191</v>
       </c>
       <c r="E15">
-        <v>-17.06738587811244</v>
+        <v>-17.59672826181705</v>
       </c>
       <c r="F15">
-        <v>-0.965001782934375</v>
+        <v>-1.032454912176936</v>
       </c>
       <c r="G15">
-        <v>-4.900677854998875</v>
+        <v>-4.654065386141947</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-17.13280162181747</v>
       </c>
       <c r="E16">
-        <v>-18.01229273607893</v>
+        <v>-18.07270257934125</v>
       </c>
       <c r="F16">
-        <v>-0.7116654936058134</v>
+        <v>-0.8121563999742271</v>
       </c>
       <c r="G16">
-        <v>-4.787622724832764</v>
+        <v>-3.78681832394677</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-16.86423408020906</v>
       </c>
       <c r="E17">
-        <v>-19.32722120521217</v>
+        <v>-18.96862946244078</v>
       </c>
       <c r="F17">
-        <v>-0.6763472210200537</v>
+        <v>-0.9051944848196535</v>
       </c>
       <c r="G17">
-        <v>-4.414153461456503</v>
+        <v>-4.154153146438762</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.66371364171552</v>
       </c>
       <c r="E18">
-        <v>-19.91740363720982</v>
+        <v>-19.91173851622623</v>
       </c>
       <c r="F18">
-        <v>-0.4220955857113987</v>
+        <v>-0.3999500115649566</v>
       </c>
       <c r="G18">
-        <v>-3.891759306996128</v>
+        <v>-3.532743885444324</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-16.5277737027092</v>
       </c>
       <c r="E19">
-        <v>-21.02962855281172</v>
+        <v>-20.65982883687134</v>
       </c>
       <c r="F19">
-        <v>-0.1874986237689674</v>
+        <v>-0.1572068845833951</v>
       </c>
       <c r="G19">
-        <v>-3.284327169268493</v>
+        <v>-3.177419722168809</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-16.44912858519486</v>
       </c>
       <c r="E20">
-        <v>-21.07802435453169</v>
+        <v>-21.46534926488174</v>
       </c>
       <c r="F20">
-        <v>0.02895295021514057</v>
+        <v>0.1358960102839595</v>
       </c>
       <c r="G20">
-        <v>-3.094258818222317</v>
+        <v>-2.783968005917507</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-16.40739559398005</v>
       </c>
       <c r="E21">
-        <v>-21.6802253565457</v>
+        <v>-21.73020612416836</v>
       </c>
       <c r="F21">
-        <v>0.1218394438258547</v>
+        <v>0.6223912157436924</v>
       </c>
       <c r="G21">
-        <v>-2.852191728390807</v>
+        <v>-3.080649165510373</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.36447640139608</v>
       </c>
       <c r="E22">
-        <v>-23.05171899450874</v>
+        <v>-22.86593834834407</v>
       </c>
       <c r="F22">
-        <v>0.6230696486465852</v>
+        <v>0.5069573897961784</v>
       </c>
       <c r="G22">
-        <v>-3.038830354258299</v>
+        <v>-2.586080146307571</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-16.28127343579239</v>
       </c>
       <c r="E23">
-        <v>-23.57490265356292</v>
+        <v>-23.19781662294421</v>
       </c>
       <c r="F23">
-        <v>0.788029904872676</v>
+        <v>0.8626724348041338</v>
       </c>
       <c r="G23">
-        <v>-3.117492226816922</v>
+        <v>-2.77318886964164</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-16.13231076116114</v>
       </c>
       <c r="E24">
-        <v>-23.61121195815642</v>
+        <v>-23.8983036248207</v>
       </c>
       <c r="F24">
-        <v>0.9884915028805451</v>
+        <v>1.07485377482681</v>
       </c>
       <c r="G24">
-        <v>-3.000163182359612</v>
+        <v>-2.512231806963049</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-15.89428777576235</v>
       </c>
       <c r="E25">
-        <v>-24.12888446434325</v>
+        <v>-24.03442502501726</v>
       </c>
       <c r="F25">
-        <v>0.8074120453633787</v>
+        <v>0.8789481975343385</v>
       </c>
       <c r="G25">
-        <v>-3.140358164856668</v>
+        <v>-2.108980875915504</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.55260372965872</v>
       </c>
       <c r="E26">
-        <v>-24.33266126621441</v>
+        <v>-23.33156510276075</v>
       </c>
       <c r="F26">
-        <v>0.9490032287890927</v>
+        <v>1.078873013465194</v>
       </c>
       <c r="G26">
-        <v>-3.350620843692399</v>
+        <v>-2.856210730675483</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.12363359587113</v>
       </c>
       <c r="E27">
-        <v>-24.65056467002688</v>
+        <v>-23.31221040485196</v>
       </c>
       <c r="F27">
-        <v>0.7013669355591945</v>
+        <v>0.8180333722020741</v>
       </c>
       <c r="G27">
-        <v>-2.801470860183633</v>
+        <v>-2.653830460768756</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.62834336560329</v>
       </c>
       <c r="E28">
-        <v>-24.43238279233732</v>
+        <v>-23.13790038334872</v>
       </c>
       <c r="F28">
-        <v>0.6560635223000895</v>
+        <v>1.188316914723064</v>
       </c>
       <c r="G28">
-        <v>-3.18940720756651</v>
+        <v>-2.697996448808173</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.08901264381448</v>
       </c>
       <c r="E29">
-        <v>-24.22885505653658</v>
+        <v>-24.3832488493541</v>
       </c>
       <c r="F29">
-        <v>0.8141417021437219</v>
+        <v>0.9258006578366785</v>
       </c>
       <c r="G29">
-        <v>-3.392363512397069</v>
+        <v>-2.265768312655388</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-13.54301721575175</v>
       </c>
       <c r="E30">
-        <v>-23.66061308110609</v>
+        <v>-23.12008989507655</v>
       </c>
       <c r="F30">
-        <v>0.9017316145809361</v>
+        <v>0.6223729916608308</v>
       </c>
       <c r="G30">
-        <v>-3.344314254440087</v>
+        <v>-2.55529207279235</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-13.02216883080694</v>
       </c>
       <c r="E31">
-        <v>-24.40272581606109</v>
+        <v>-23.2607488262288</v>
       </c>
       <c r="F31">
-        <v>0.8009557498259594</v>
+        <v>0.9024970260611228</v>
       </c>
       <c r="G31">
-        <v>-3.33671324188192</v>
+        <v>-2.674051272922625</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-12.54321212763994</v>
       </c>
       <c r="E32">
-        <v>-23.95532616952528</v>
+        <v>-23.56688272609533</v>
       </c>
       <c r="F32">
-        <v>0.7039423298144981</v>
+        <v>0.5586301200154088</v>
       </c>
       <c r="G32">
-        <v>-3.039585158641253</v>
+        <v>-2.430842044880067</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-12.12154853866636</v>
       </c>
       <c r="E33">
-        <v>-23.92447820458503</v>
+        <v>-22.57792740145623</v>
       </c>
       <c r="F33">
-        <v>0.495324626358665</v>
+        <v>0.5018107431225851</v>
       </c>
       <c r="G33">
-        <v>-2.936292827270452</v>
+        <v>-2.441058388414258</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.76533829056064</v>
       </c>
       <c r="E34">
-        <v>-22.79079737913479</v>
+        <v>-23.01996533476696</v>
       </c>
       <c r="F34">
-        <v>0.7956873331441545</v>
+        <v>0.4650867310542747</v>
       </c>
       <c r="G34">
-        <v>-2.363015587871479</v>
+        <v>-2.02174137986463</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.46715136071093</v>
       </c>
       <c r="E35">
-        <v>-22.76565529144421</v>
+        <v>-22.09135192628007</v>
       </c>
       <c r="F35">
-        <v>0.8238435411653098</v>
+        <v>0.5892142728941694</v>
       </c>
       <c r="G35">
-        <v>-3.803652448013964</v>
+        <v>-1.357761813780704</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.21503001336147</v>
       </c>
       <c r="E36">
-        <v>-22.6033547830093</v>
+        <v>-22.44519782829141</v>
       </c>
       <c r="F36">
-        <v>0.5460786971281907</v>
+        <v>0.6336520422173488</v>
       </c>
       <c r="G36">
-        <v>-2.668936480064451</v>
+        <v>-1.976327316156908</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.00559268784856</v>
       </c>
       <c r="E37">
-        <v>-22.41979308910838</v>
+        <v>-21.34831991110152</v>
       </c>
       <c r="F37">
-        <v>0.6754249536057223</v>
+        <v>0.6013308028949178</v>
       </c>
       <c r="G37">
-        <v>-2.249470496965556</v>
+        <v>-1.607148519799542</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.8303890490355</v>
       </c>
       <c r="E38">
-        <v>-21.28684134797338</v>
+        <v>-21.06815228119497</v>
       </c>
       <c r="F38">
-        <v>0.6259225459818267</v>
+        <v>0.2457491250388132</v>
       </c>
       <c r="G38">
-        <v>-2.517694207102847</v>
+        <v>-1.842117799994854</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.68052209847644</v>
       </c>
       <c r="E39">
-        <v>-21.28823158949374</v>
+        <v>-20.6428561162906</v>
       </c>
       <c r="F39">
-        <v>0.5110238453765212</v>
+        <v>0.3735032593681641</v>
       </c>
       <c r="G39">
-        <v>-2.296632528718013</v>
+        <v>-1.281188895457362</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.56574282494672</v>
       </c>
       <c r="E40">
-        <v>-20.97155993061136</v>
+        <v>-20.57137415407952</v>
       </c>
       <c r="F40">
-        <v>0.5440309729084704</v>
+        <v>0.284892798290701</v>
       </c>
       <c r="G40">
-        <v>-2.44945393190185</v>
+        <v>-1.093669664476424</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-10.492224952205</v>
       </c>
       <c r="E41">
-        <v>-19.73209848081595</v>
+        <v>-20.11476359141211</v>
       </c>
       <c r="F41">
-        <v>0.4743346247391284</v>
+        <v>0.4864660653531271</v>
       </c>
       <c r="G41">
-        <v>-2.235129213689433</v>
+        <v>-0.9620920320180907</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-10.46306186746062</v>
       </c>
       <c r="E42">
-        <v>-19.52314563315402</v>
+        <v>-19.44296447237421</v>
       </c>
       <c r="F42">
-        <v>0.6678304812568565</v>
+        <v>0.3907498686944498</v>
       </c>
       <c r="G42">
-        <v>-1.454194694794135</v>
+        <v>-0.8068307567718113</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-10.49189009886319</v>
       </c>
       <c r="E43">
-        <v>-19.49763673906882</v>
+        <v>-18.74191141124676</v>
       </c>
       <c r="F43">
-        <v>0.7254815390220909</v>
+        <v>0.1663683335633422</v>
       </c>
       <c r="G43">
-        <v>-1.519511758283955</v>
+        <v>-0.5455161551749794</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-10.58533150093093</v>
       </c>
       <c r="E44">
-        <v>-18.15143462843861</v>
+        <v>-18.5949262019058</v>
       </c>
       <c r="F44">
-        <v>0.6794615879595644</v>
+        <v>0.09489099547798122</v>
       </c>
       <c r="G44">
-        <v>-1.447421318620786</v>
+        <v>-0.6126209132560063</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.73873426848719</v>
       </c>
       <c r="E45">
-        <v>-18.79345450240207</v>
+        <v>-18.29332530452095</v>
       </c>
       <c r="F45">
-        <v>0.8361464538316881</v>
+        <v>0.02694912946776857</v>
       </c>
       <c r="G45">
-        <v>-1.626124566830645</v>
+        <v>-0.7644955004156113</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.95271471251544</v>
       </c>
       <c r="E46">
-        <v>-18.11251692281669</v>
+        <v>-17.14266723001596</v>
       </c>
       <c r="F46">
-        <v>0.3586854232668866</v>
+        <v>0.2625318486195312</v>
       </c>
       <c r="G46">
-        <v>-1.624257419146496</v>
+        <v>-0.6300310722470335</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.22430763531708</v>
       </c>
       <c r="E47">
-        <v>-17.04782287039931</v>
+        <v>-16.79994326016745</v>
       </c>
       <c r="F47">
-        <v>0.5019432819070331</v>
+        <v>0.042300434176449</v>
       </c>
       <c r="G47">
-        <v>-1.510659359511944</v>
+        <v>-0.4887535413586356</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.53882198802756</v>
       </c>
       <c r="E48">
-        <v>-17.24150117523336</v>
+        <v>-16.89822020308191</v>
       </c>
       <c r="F48">
-        <v>0.3779723015062675</v>
+        <v>0.0493349301610224</v>
       </c>
       <c r="G48">
-        <v>-1.669949568679517</v>
+        <v>-0.6657948957077802</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.88460623493687</v>
       </c>
       <c r="E49">
-        <v>-16.91525179382476</v>
+        <v>-15.8135555802907</v>
       </c>
       <c r="F49">
-        <v>0.2294451978169133</v>
+        <v>-0.08818234237772353</v>
       </c>
       <c r="G49">
-        <v>-2.121653644239835</v>
+        <v>-0.369355405939281</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.25670451074539</v>
       </c>
       <c r="E50">
-        <v>-15.82938259694751</v>
+        <v>-16.23497084297049</v>
       </c>
       <c r="F50">
-        <v>0.1515811470559682</v>
+        <v>-0.2833092543115638</v>
       </c>
       <c r="G50">
-        <v>-1.549521853597449</v>
+        <v>-0.9514089015628625</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.64257028199992</v>
       </c>
       <c r="E51">
-        <v>-14.84120616983773</v>
+        <v>-14.87819474553238</v>
       </c>
       <c r="F51">
-        <v>-0.02324993514188147</v>
+        <v>-0.5099572026567309</v>
       </c>
       <c r="G51">
-        <v>-2.008356844249357</v>
+        <v>-0.5418083441709957</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-13.02941351785298</v>
       </c>
       <c r="E52">
-        <v>-14.74907436615167</v>
+        <v>-15.51690883347024</v>
       </c>
       <c r="F52">
-        <v>0.1835047700250555</v>
+        <v>0.0451491896746765</v>
       </c>
       <c r="G52">
-        <v>-2.28765101866997</v>
+        <v>-1.208005975766233</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-13.41798694424558</v>
       </c>
       <c r="E53">
-        <v>-14.098074528231</v>
+        <v>-14.64697991964874</v>
       </c>
       <c r="F53">
-        <v>0.1159439530201306</v>
+        <v>-0.1195608995957688</v>
       </c>
       <c r="G53">
-        <v>-1.772444058575352</v>
+        <v>-0.9130661631270237</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-13.80255225969986</v>
       </c>
       <c r="E54">
-        <v>-13.20075740361112</v>
+        <v>-14.23733868938889</v>
       </c>
       <c r="F54">
-        <v>0.07136867470808646</v>
+        <v>-0.2989529727134325</v>
       </c>
       <c r="G54">
-        <v>-2.279805025741898</v>
+        <v>-1.328413827575065</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.17118884290698</v>
       </c>
       <c r="E55">
-        <v>-13.69169379925667</v>
+        <v>-14.67194086837902</v>
       </c>
       <c r="F55">
-        <v>0.2790171883026441</v>
+        <v>-0.1629847472179217</v>
       </c>
       <c r="G55">
-        <v>-2.078623173320388</v>
+        <v>-1.309659587095094</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-14.52568553290191</v>
       </c>
       <c r="E56">
-        <v>-12.63697597507819</v>
+        <v>-13.68985976728357</v>
       </c>
       <c r="F56">
-        <v>0.08850179770018862</v>
+        <v>-0.2341183128311208</v>
       </c>
       <c r="G56">
-        <v>-3.091941436344827</v>
+        <v>-1.954186387590262</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-14.86199680213449</v>
       </c>
       <c r="E57">
-        <v>-12.04362361127516</v>
+        <v>-12.82759755995706</v>
       </c>
       <c r="F57">
-        <v>0.003412726452026211</v>
+        <v>-0.3218946079339648</v>
       </c>
       <c r="G57">
-        <v>-3.079672554576288</v>
+        <v>-1.62669067011786</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.16739036812461</v>
       </c>
       <c r="E58">
-        <v>-12.7132626482114</v>
+        <v>-12.68101538480278</v>
       </c>
       <c r="F58">
-        <v>0.007960463493395497</v>
+        <v>-0.2541730876528969</v>
       </c>
       <c r="G58">
-        <v>-3.729118825742813</v>
+        <v>-1.968676645415652</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.43729994390142</v>
       </c>
       <c r="E59">
-        <v>-12.44820200759444</v>
+        <v>-11.88906679339337</v>
       </c>
       <c r="F59">
-        <v>0.1355613498532285</v>
+        <v>-0.2605921066571902</v>
       </c>
       <c r="G59">
-        <v>-3.642074651878755</v>
+        <v>-2.236632201364262</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-15.66598179848569</v>
       </c>
       <c r="E60">
-        <v>-11.61471825258668</v>
+        <v>-12.19451689368475</v>
       </c>
       <c r="F60">
-        <v>-0.001501148981380456</v>
+        <v>-0.4705525936729613</v>
       </c>
       <c r="G60">
-        <v>-3.119173983950871</v>
+        <v>-2.708067128338636</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-15.8409720514917</v>
       </c>
       <c r="E61">
-        <v>-11.32377285454188</v>
+        <v>-11.74634287809363</v>
       </c>
       <c r="F61">
-        <v>-0.02581704572315715</v>
+        <v>-0.3881441193402581</v>
       </c>
       <c r="G61">
-        <v>-3.744582383956748</v>
+        <v>-2.681652285480791</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-15.95339265954669</v>
       </c>
       <c r="E62">
-        <v>-10.7329292653391</v>
+        <v>-10.30084038942323</v>
       </c>
       <c r="F62">
-        <v>-0.2101486736637143</v>
+        <v>-0.3668633607623388</v>
       </c>
       <c r="G62">
-        <v>-4.613501271649257</v>
+        <v>-2.85136409200599</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.00596762173468</v>
       </c>
       <c r="E63">
-        <v>-10.22653718790537</v>
+        <v>-10.95850614108318</v>
       </c>
       <c r="F63">
-        <v>-0.3128123877296711</v>
+        <v>-0.5318062212729707</v>
       </c>
       <c r="G63">
-        <v>-4.25359862389293</v>
+        <v>-2.359125696862835</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-15.99751089343961</v>
       </c>
       <c r="E64">
-        <v>-9.935904254567095</v>
+        <v>-10.78170545887572</v>
       </c>
       <c r="F64">
-        <v>-0.2655208927038473</v>
+        <v>-0.701532075167367</v>
       </c>
       <c r="G64">
-        <v>-4.483949693060958</v>
+        <v>-3.166643896438481</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-15.9271093999307</v>
       </c>
       <c r="E65">
-        <v>-9.57488072125359</v>
+        <v>-10.07484236559643</v>
       </c>
       <c r="F65">
-        <v>-0.3360099884776684</v>
+        <v>-0.657890366918278</v>
       </c>
       <c r="G65">
-        <v>-4.751286176993724</v>
+        <v>-3.27589520977997</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-15.81051130777091</v>
       </c>
       <c r="E66">
-        <v>-9.481408489261268</v>
+        <v>-10.53543798539059</v>
       </c>
       <c r="F66">
-        <v>-0.3204060317111341</v>
+        <v>-0.5478840041939064</v>
       </c>
       <c r="G66">
-        <v>-4.396733370828859</v>
+        <v>-3.566220121937435</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-15.65997947898722</v>
       </c>
       <c r="E67">
-        <v>-9.753687517446455</v>
+        <v>-10.39408619771517</v>
       </c>
       <c r="F67">
-        <v>-0.2227108653271688</v>
+        <v>-0.9868483164484064</v>
       </c>
       <c r="G67">
-        <v>-4.753179809042187</v>
+        <v>-3.51822714325462</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-15.48168969803163</v>
       </c>
       <c r="E68">
-        <v>-8.742112465139042</v>
+        <v>-10.89570979201882</v>
       </c>
       <c r="F68">
-        <v>-0.5320505896567966</v>
+        <v>-1.007784474186761</v>
       </c>
       <c r="G68">
-        <v>-5.400080270689013</v>
+        <v>-3.332757139962491</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.29433954908215</v>
       </c>
       <c r="E69">
-        <v>-8.524111726409792</v>
+        <v>-10.3245605362754</v>
       </c>
       <c r="F69">
-        <v>-0.4017906439339772</v>
+        <v>-0.7837044647902724</v>
       </c>
       <c r="G69">
-        <v>-4.691732773287774</v>
+        <v>-3.166925292809319</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.11095247538878</v>
       </c>
       <c r="E70">
-        <v>-9.547836674479784</v>
+        <v>-10.56315224631753</v>
       </c>
       <c r="F70">
-        <v>-0.3594246214851992</v>
+        <v>-1.030456061633981</v>
       </c>
       <c r="G70">
-        <v>-4.862424501292597</v>
+        <v>-3.287300039162758</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-14.93251509889064</v>
       </c>
       <c r="E71">
-        <v>-8.948561066674728</v>
+        <v>-10.27061282542203</v>
       </c>
       <c r="F71">
-        <v>-0.7722473152421525</v>
+        <v>-1.051431152640267</v>
       </c>
       <c r="G71">
-        <v>-5.181590886188193</v>
+        <v>-3.739242474001904</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.76346936133837</v>
       </c>
       <c r="E72">
-        <v>-8.875389983658788</v>
+        <v>-10.39799427078379</v>
       </c>
       <c r="F72">
-        <v>-0.6028644054525152</v>
+        <v>-1.002237726057616</v>
       </c>
       <c r="G72">
-        <v>-4.13508440413256</v>
+        <v>-3.369643238361051</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.60964430039388</v>
       </c>
       <c r="E73">
-        <v>-8.732100009108084</v>
+        <v>-9.151989176047294</v>
       </c>
       <c r="F73">
-        <v>-0.6196587261768723</v>
+        <v>-1.110233641095393</v>
       </c>
       <c r="G73">
-        <v>-4.221807455079308</v>
+        <v>-3.552408525947595</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.46687123479695</v>
       </c>
       <c r="E74">
-        <v>-10.17063317628068</v>
+        <v>-10.38280124048805</v>
       </c>
       <c r="F74">
-        <v>-0.4997318354365739</v>
+        <v>-1.35794365902414</v>
       </c>
       <c r="G74">
-        <v>-4.698463112369113</v>
+        <v>-3.484611863848861</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-14.32830648930112</v>
       </c>
       <c r="E75">
-        <v>-10.47131479344198</v>
+        <v>-10.92166700503079</v>
       </c>
       <c r="F75">
-        <v>-0.7135400890383486</v>
+        <v>-1.218420080635814</v>
       </c>
       <c r="G75">
-        <v>-4.210084813324749</v>
+        <v>-2.738550631664245</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-14.19866772179925</v>
       </c>
       <c r="E76">
-        <v>-10.3801113269275</v>
+        <v>-10.6681041599193</v>
       </c>
       <c r="F76">
-        <v>-1.084723238558779</v>
+        <v>-1.444476574655382</v>
       </c>
       <c r="G76">
-        <v>-4.035400567399565</v>
+        <v>-3.329208235144393</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-14.07451731752527</v>
       </c>
       <c r="E77">
-        <v>-9.99770886782378</v>
+        <v>-11.37859456087873</v>
       </c>
       <c r="F77">
-        <v>-0.7976193804224985</v>
+        <v>-1.484059282630754</v>
       </c>
       <c r="G77">
-        <v>-3.614540844628637</v>
+        <v>-3.124047106984678</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-13.94822029285678</v>
       </c>
       <c r="E78">
-        <v>-10.4911042248555</v>
+        <v>-11.45300644577277</v>
       </c>
       <c r="F78">
-        <v>-0.9050776850158588</v>
+        <v>-1.615915492338768</v>
       </c>
       <c r="G78">
-        <v>-3.631752370887308</v>
+        <v>-2.444984695423833</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-13.82705717109023</v>
       </c>
       <c r="E79">
-        <v>-11.27163653329157</v>
+        <v>-12.73753526889251</v>
       </c>
       <c r="F79">
-        <v>-0.9607754524452919</v>
+        <v>-1.626124292210869</v>
       </c>
       <c r="G79">
-        <v>-3.663483949881222</v>
+        <v>-2.711119451325844</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-13.71261053729084</v>
       </c>
       <c r="E80">
-        <v>-11.98169672922027</v>
+        <v>-11.99920833820793</v>
       </c>
       <c r="F80">
-        <v>-1.274314999507113</v>
+        <v>-1.618417161895222</v>
       </c>
       <c r="G80">
-        <v>-3.688859281439736</v>
+        <v>-2.897711729555786</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-13.59775596302526</v>
       </c>
       <c r="E81">
-        <v>-12.40409467075973</v>
+        <v>-12.80942026529027</v>
       </c>
       <c r="F81">
-        <v>-1.46485441276425</v>
+        <v>-1.779052511911297</v>
       </c>
       <c r="G81">
-        <v>-3.32049818983057</v>
+        <v>-2.629673409968694</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-13.48932551059772</v>
       </c>
       <c r="E82">
-        <v>-13.20482850174402</v>
+        <v>-14.06035233974711</v>
       </c>
       <c r="F82">
-        <v>-1.37901732575136</v>
+        <v>-2.027893251344866</v>
       </c>
       <c r="G82">
-        <v>-3.306620382929945</v>
+        <v>-2.373298142316455</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-13.39302067760489</v>
       </c>
       <c r="E83">
-        <v>-13.72534036113367</v>
+        <v>-15.01989069723238</v>
       </c>
       <c r="F83">
-        <v>-1.550182882191821</v>
+        <v>-2.005799035977397</v>
       </c>
       <c r="G83">
-        <v>-3.116899639165392</v>
+        <v>-1.880513507159321</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-13.30757425315625</v>
       </c>
       <c r="E84">
-        <v>-15.06952277235645</v>
+        <v>-15.2857528777487</v>
       </c>
       <c r="F84">
-        <v>-1.595627946276805</v>
+        <v>-2.142304043549922</v>
       </c>
       <c r="G84">
-        <v>-2.51263900406438</v>
+        <v>-1.857233750927166</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-13.23822377309903</v>
       </c>
       <c r="E85">
-        <v>-15.53022707552679</v>
+        <v>-16.20050915577212</v>
       </c>
       <c r="F85">
-        <v>-1.674935013053427</v>
+        <v>-2.400617992601906</v>
       </c>
       <c r="G85">
-        <v>-2.392721112995359</v>
+        <v>-1.878705949294879</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-13.19365839755188</v>
       </c>
       <c r="E86">
-        <v>-16.67956283562155</v>
+        <v>-18.35450045989057</v>
       </c>
       <c r="F86">
-        <v>-1.964257239094405</v>
+        <v>-2.395598086140941</v>
       </c>
       <c r="G86">
-        <v>-2.17818120932289</v>
+        <v>-1.597928650472672</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-13.17404411881657</v>
       </c>
       <c r="E87">
-        <v>-18.08424565958681</v>
+        <v>-18.16549554023243</v>
       </c>
       <c r="F87">
-        <v>-1.948258979444138</v>
+        <v>-2.220434000247166</v>
       </c>
       <c r="G87">
-        <v>-2.209217573753557</v>
+        <v>-1.301379912701377</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-13.17873525015384</v>
       </c>
       <c r="E88">
-        <v>-19.94162191620284</v>
+        <v>-19.59182446995435</v>
       </c>
       <c r="F88">
-        <v>-2.138264095726469</v>
+        <v>-2.58373854739957</v>
       </c>
       <c r="G88">
-        <v>-2.568967936415079</v>
+        <v>-1.358824498898811</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.21938309650753</v>
       </c>
       <c r="E89">
-        <v>-21.15945084566361</v>
+        <v>-21.3584048227166</v>
       </c>
       <c r="F89">
-        <v>-2.178425832516397</v>
+        <v>-2.553436039437762</v>
       </c>
       <c r="G89">
-        <v>-2.006744608571732</v>
+        <v>-1.767769568273902</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.29851008400789</v>
       </c>
       <c r="E90">
-        <v>-23.38825706886277</v>
+        <v>-23.41256591733595</v>
       </c>
       <c r="F90">
-        <v>-2.552855353888399</v>
+        <v>-2.69006944395772</v>
       </c>
       <c r="G90">
-        <v>-1.750111118367429</v>
+        <v>-1.322977911799582</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.41392723090106</v>
       </c>
       <c r="E91">
-        <v>-23.88572352402739</v>
+        <v>-25.15857794115535</v>
       </c>
       <c r="F91">
-        <v>-2.485051825234454</v>
+        <v>-2.774359969029584</v>
       </c>
       <c r="G91">
-        <v>-2.410048508347905</v>
+        <v>-1.751624037678876</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-13.57735457642238</v>
       </c>
       <c r="E92">
-        <v>-25.68448321308814</v>
+        <v>-26.47454795931035</v>
       </c>
       <c r="F92">
-        <v>-2.598152140208282</v>
+        <v>-2.823872317062313</v>
       </c>
       <c r="G92">
-        <v>-1.772943950951783</v>
+        <v>-0.9046375141840393</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-13.79287617735969</v>
       </c>
       <c r="E93">
-        <v>-27.65170213523422</v>
+        <v>-28.3845360269475</v>
       </c>
       <c r="F93">
-        <v>-2.4632873000933</v>
+        <v>-3.101696803552434</v>
       </c>
       <c r="G93">
-        <v>-2.7611980736984</v>
+        <v>-1.823075542052966</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-14.05293497316122</v>
       </c>
       <c r="E94">
-        <v>-29.9267395495777</v>
+        <v>-30.13542068879916</v>
       </c>
       <c r="F94">
-        <v>-2.639988835886671</v>
+        <v>-2.918920021226931</v>
       </c>
       <c r="G94">
-        <v>-2.492964431924491</v>
+        <v>-1.81020083045074</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-14.36143060509333</v>
       </c>
       <c r="E95">
-        <v>-32.66498551321775</v>
+        <v>-33.29528343221236</v>
       </c>
       <c r="F95">
-        <v>-2.624141339103713</v>
+        <v>-2.929659804604227</v>
       </c>
       <c r="G95">
-        <v>-3.088644132987713</v>
+        <v>-1.826458919594101</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-14.71550170820382</v>
       </c>
       <c r="E96">
-        <v>-34.17707015522294</v>
+        <v>-34.74589856803742</v>
       </c>
       <c r="F96">
-        <v>-2.680647593118278</v>
+        <v>-3.232671630343869</v>
       </c>
       <c r="G96">
-        <v>-2.853850311705982</v>
+        <v>-2.087667583733677</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-15.09532068535142</v>
       </c>
       <c r="E97">
-        <v>-37.42790541297622</v>
+        <v>-37.56488495899723</v>
       </c>
       <c r="F97">
-        <v>-2.66738294589725</v>
+        <v>-3.073767568199646</v>
       </c>
       <c r="G97">
-        <v>-3.253939671763523</v>
+        <v>-2.540444276048718</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-15.49156916437483</v>
       </c>
       <c r="E98">
-        <v>-40.20263049898507</v>
+        <v>-39.21891688300985</v>
       </c>
       <c r="F98">
-        <v>-2.633531711981848</v>
+        <v>-2.808645267464053</v>
       </c>
       <c r="G98">
-        <v>-3.290706590522669</v>
+        <v>-3.226167505234577</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-15.88261472140005</v>
       </c>
       <c r="E99">
-        <v>-42.727673642107</v>
+        <v>-42.13906711906401</v>
       </c>
       <c r="F99">
-        <v>-2.757910249144791</v>
+        <v>-3.168916333187405</v>
       </c>
       <c r="G99">
-        <v>-3.907179828118053</v>
+        <v>-2.968921564105509</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.25544302824218</v>
       </c>
       <c r="E100">
-        <v>-45.3606235281207</v>
+        <v>-45.0143605558352</v>
       </c>
       <c r="F100">
-        <v>-2.470813846315136</v>
+        <v>-2.958947562497606</v>
       </c>
       <c r="G100">
-        <v>-4.34271519926457</v>
+        <v>-3.221056022921942</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.56485690611438</v>
       </c>
       <c r="E101">
-        <v>-48.29728684464384</v>
+        <v>-48.08858759152635</v>
       </c>
       <c r="F101">
-        <v>-2.579715166924173</v>
+        <v>-2.984790968730145</v>
       </c>
       <c r="G101">
-        <v>-4.729939779356503</v>
+        <v>-3.794644453601607</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.8287661341322</v>
       </c>
       <c r="E102">
-        <v>-50.55370543810478</v>
+        <v>-49.91098251855163</v>
       </c>
       <c r="F102">
-        <v>-2.636207338692891</v>
+        <v>-3.014864018921378</v>
       </c>
       <c r="G102">
-        <v>-4.540162756317782</v>
+        <v>-3.538232769948436</v>
       </c>
     </row>
   </sheetData>
